--- a/Test_Data1.xlsx
+++ b/Test_Data1.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t xml:space="preserve">FName</t>
   </si>
@@ -125,9 +125,6 @@
   </si>
   <si>
     <t xml:space="preserve">xcvbnm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jyoti</t>
   </si>
 </sst>
 </file>
@@ -389,59 +386,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="N3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="O3" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
+    <row r="1048541" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048542" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048543" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048544" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -476,11 +421,10 @@
     <row r="1048573" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048574" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1048575" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="H2" r:id="rId1" display="shivendra.shrivastava@corecard.com"/>
-    <hyperlink ref="H3" r:id="rId2" display="shivendra.shrivastava@corecard.com"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
